--- a/trust/CodeSystem-Transactions.xlsx
+++ b/trust/CodeSystem-Transactions.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-27T08:38:34+00:00</t>
+    <t>2026-02-11T14:17:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/CodeSystem-Transactions.xlsx
+++ b/trust/CodeSystem-Transactions.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.4.0</t>
+    <t>1.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T14:17:30+00:00</t>
+    <t>2026-04-27T07:32:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/CodeSystem-Transactions.xlsx
+++ b/trust/CodeSystem-Transactions.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-27T07:32:49+00:00</t>
+    <t>2026-07-03T08:24:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/CodeSystem-Transactions.xlsx
+++ b/trust/CodeSystem-Transactions.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T08:24:29+00:00</t>
+    <t>2026-07-06T11:52:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/CodeSystem-Transactions.xlsx
+++ b/trust/CodeSystem-Transactions.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.6.0</t>
+    <t>1.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T11:52:41+00:00</t>
+    <t>2026-07-30T11:57:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/CodeSystem-Transactions.xlsx
+++ b/trust/CodeSystem-Transactions.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.7.0</t>
+    <t>1.7.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T11:57:48+00:00</t>
+    <t>2026-08-27T05:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/CodeSystem-Transactions.xlsx
+++ b/trust/CodeSystem-Transactions.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.7.1</t>
+    <t>1.7.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T05:52:17+00:00</t>
+    <t>2026-09-03T12:39:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
